--- a/연구코드/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/all/regression_results.xlsx
@@ -1,39 +1,143 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <workbookPr/>
-  <workbookProtection/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+  <workbookPr defaultThemeVersion="124226"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="linear_fold_r2" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="logistic_fold_auc" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="summary" sheetId="1" r:id="rId1"/>
+    <sheet name="linear_fold_r2" sheetId="2" r:id="rId2"/>
+    <sheet name="logistic_fold_auc" sheetId="3" r:id="rId3"/>
   </sheets>
-  <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+  <si>
+    <t>Hospital</t>
+  </si>
+  <si>
+    <t>Sex</t>
+  </si>
+  <si>
+    <t>Case</t>
+  </si>
+  <si>
+    <t>N_features</t>
+  </si>
+  <si>
+    <t>N_rows</t>
+  </si>
+  <si>
+    <t>Lin_R2</t>
+  </si>
+  <si>
+    <t>Lin_R2_std</t>
+  </si>
+  <si>
+    <t>Lin_MAE</t>
+  </si>
+  <si>
+    <t>Lin_RMSE</t>
+  </si>
+  <si>
+    <t>TAMA_threshold</t>
+  </si>
+  <si>
+    <t>Log_AUC</t>
+  </si>
+  <si>
+    <t>Log_AUC_std</t>
+  </si>
+  <si>
+    <t>Log_Acc</t>
+  </si>
+  <si>
+    <t>Log_Sens</t>
+  </si>
+  <si>
+    <t>Log_Spec</t>
+  </si>
+  <si>
+    <t>강남</t>
+  </si>
+  <si>
+    <t>전체</t>
+  </si>
+  <si>
+    <t>Case 1 Clinical</t>
+  </si>
+  <si>
+    <t>Case 2 +AEC_prev</t>
+  </si>
+  <si>
+    <t>Case 3 +AEC_new</t>
+  </si>
+  <si>
+    <t>Case 4 +AEC_prev +Scanner</t>
+  </si>
+  <si>
+    <t>Case 5 +AEC_new +Scanner</t>
+  </si>
+  <si>
+    <t>Case1_Clinical</t>
+  </si>
+  <si>
+    <t>Case2_Clinical+AEC_prev</t>
+  </si>
+  <si>
+    <t>Case3_Clinical+AEC_new</t>
+  </si>
+  <si>
+    <t>Case4_Clinical+AEC_prev+Scanner</t>
+  </si>
+  <si>
+    <t>Case5_Clinical+AEC_new+Scanner</t>
+  </si>
+  <si>
+    <t>Fold1</t>
+  </si>
+  <si>
+    <t>Fold2</t>
+  </si>
+  <si>
+    <t>Fold3</t>
+  </si>
+  <si>
+    <t>Fold4</t>
+  </si>
+  <si>
+    <t>Fold5</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
   <fonts count="2">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b val="1"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -48,93 +152,35 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
 </styleSheet>
 </file>
 
@@ -422,659 +468,547 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:O6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Hospital</t>
-        </is>
-      </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Sex</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Case</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>N_features</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>N_rows</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_R2</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_R2_std</t>
-        </is>
-      </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_MAE</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Lin_RMSE</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
-        <is>
-          <t>TAMA_threshold</t>
-        </is>
-      </c>
-      <c r="K1" s="1" t="inlineStr">
-        <is>
-          <t>Log_AUC</t>
-        </is>
-      </c>
-      <c r="L1" s="1" t="inlineStr">
-        <is>
-          <t>Log_AUC_std</t>
-        </is>
-      </c>
-      <c r="M1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Acc</t>
-        </is>
-      </c>
-      <c r="N1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Sens</t>
-        </is>
-      </c>
-      <c r="O1" s="1" t="inlineStr">
-        <is>
-          <t>Log_Spec</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Case 1 Clinical</t>
-        </is>
-      </c>
-      <c r="D2" t="n">
+    <row r="1" spans="1:15">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:15">
+      <c r="A2" t="s">
+        <v>15</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2">
+        <v>3</v>
+      </c>
+      <c r="E2">
         <v>1365</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.662</v>
       </c>
-      <c r="G2" t="n">
+      <c r="G2">
         <v>0.0367</v>
       </c>
-      <c r="H2" t="n">
+      <c r="H2">
         <v>12.83</v>
       </c>
-      <c r="I2" t="n">
+      <c r="I2">
         <v>17.12</v>
       </c>
-      <c r="J2" t="n">
+      <c r="J2">
         <v>100</v>
       </c>
-      <c r="K2" t="n">
+      <c r="K2">
         <v>0.8293</v>
       </c>
-      <c r="L2" t="n">
+      <c r="L2">
         <v>0.0208</v>
       </c>
-      <c r="M2" t="n">
+      <c r="M2">
         <v>0.7868000000000001</v>
       </c>
-      <c r="N2" t="n">
+      <c r="N2">
         <v>0.3414</v>
       </c>
-      <c r="O2" t="n">
+      <c r="O2">
         <v>0.9243</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Case 2 +AEC_prev</t>
-        </is>
-      </c>
-      <c r="D3" t="n">
+    <row r="3" spans="1:15">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+      <c r="C3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D3">
         <v>7</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>1365</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.678</v>
       </c>
-      <c r="G3" t="n">
+      <c r="G3">
         <v>0.0357</v>
       </c>
-      <c r="H3" t="n">
+      <c r="H3">
         <v>12.53</v>
       </c>
-      <c r="I3" t="n">
+      <c r="I3">
         <v>16.71</v>
       </c>
-      <c r="J3" t="n">
+      <c r="J3">
         <v>100</v>
       </c>
-      <c r="K3" t="n">
+      <c r="K3">
         <v>0.8346</v>
       </c>
-      <c r="L3" t="n">
+      <c r="L3">
         <v>0.0247</v>
       </c>
-      <c r="M3" t="n">
+      <c r="M3">
         <v>0.7846</v>
       </c>
-      <c r="N3" t="n">
+      <c r="N3">
         <v>0.3447</v>
       </c>
-      <c r="O3" t="n">
+      <c r="O3">
         <v>0.9204</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Case 3 +AEC_new</t>
-        </is>
-      </c>
-      <c r="D4" t="n">
+    <row r="4" spans="1:15">
+      <c r="A4" t="s">
+        <v>15</v>
+      </c>
+      <c r="B4" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" t="s">
+        <v>19</v>
+      </c>
+      <c r="D4">
         <v>14</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>1365</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.6694</v>
       </c>
-      <c r="G4" t="n">
+      <c r="G4">
         <v>0.0385</v>
       </c>
-      <c r="H4" t="n">
+      <c r="H4">
         <v>12.59</v>
       </c>
-      <c r="I4" t="n">
+      <c r="I4">
         <v>16.93</v>
       </c>
-      <c r="J4" t="n">
+      <c r="J4">
         <v>100</v>
       </c>
-      <c r="K4" t="n">
+      <c r="K4">
         <v>0.8352000000000001</v>
       </c>
-      <c r="L4" t="n">
+      <c r="L4">
         <v>0.0229</v>
       </c>
-      <c r="M4" t="n">
+      <c r="M4">
         <v>0.7853</v>
       </c>
-      <c r="N4" t="n">
+      <c r="N4">
         <v>0.3571</v>
       </c>
-      <c r="O4" t="n">
+      <c r="O4">
         <v>0.9175</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Case 4 +AEC_prev +Scanner</t>
-        </is>
-      </c>
-      <c r="D5" t="n">
+    <row r="5" spans="1:15">
+      <c r="A5" t="s">
+        <v>15</v>
+      </c>
+      <c r="B5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D5">
         <v>46</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>1365</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.6682</v>
       </c>
-      <c r="G5" t="n">
+      <c r="G5">
         <v>0.0318</v>
       </c>
-      <c r="H5" t="n">
+      <c r="H5">
         <v>12.77</v>
       </c>
-      <c r="I5" t="n">
+      <c r="I5">
         <v>16.96</v>
       </c>
-      <c r="J5" t="n">
+      <c r="J5">
         <v>100</v>
       </c>
-      <c r="K5" t="n">
+      <c r="K5">
         <v>0.8306</v>
       </c>
-      <c r="L5" t="n">
+      <c r="L5">
         <v>0.0209</v>
       </c>
-      <c r="M5" t="n">
+      <c r="M5">
         <v>0.7883</v>
       </c>
-      <c r="N5" t="n">
+      <c r="N5">
         <v>0.3758</v>
       </c>
-      <c r="O5" t="n">
+      <c r="O5">
         <v>0.9156</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>강남</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>전체</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Case 5 +AEC_new +Scanner</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
+    <row r="6" spans="1:15">
+      <c r="A6" t="s">
+        <v>15</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>21</v>
+      </c>
+      <c r="D6">
         <v>53</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>1365</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.662</v>
       </c>
-      <c r="G6" t="n">
+      <c r="G6">
         <v>0.0353</v>
       </c>
-      <c r="H6" t="n">
+      <c r="H6">
         <v>12.74</v>
       </c>
-      <c r="I6" t="n">
+      <c r="I6">
         <v>17.11</v>
       </c>
-      <c r="J6" t="n">
+      <c r="J6">
         <v>100</v>
       </c>
-      <c r="K6" t="n">
+      <c r="K6">
         <v>0.832</v>
       </c>
-      <c r="L6" t="n">
+      <c r="L6">
         <v>0.0182</v>
       </c>
-      <c r="M6" t="n">
+      <c r="M6">
         <v>0.7941</v>
       </c>
-      <c r="N6" t="n">
+      <c r="N6">
         <v>0.3913</v>
       </c>
-      <c r="O6" t="n">
+      <c r="O6">
         <v>0.9185</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Case1_Clinical</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Case2_Clinical+AEC_prev</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Case3_Clinical+AEC_new</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Case4_Clinical+AEC_prev+Scanner</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Case5_Clinical+AEC_new+Scanner</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Fold1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6">
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
         <v>0.6734344380268682</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.6702630916927976</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.6616180339311908</v>
       </c>
-      <c r="E2" t="n">
-        <v>0.675732316735406</v>
-      </c>
-      <c r="F2" t="n">
-        <v>0.6585903231162165</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Fold2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+      <c r="E2">
+        <v>0.6757323167354061</v>
+      </c>
+      <c r="F2">
+        <v>0.6585903231162162</v>
+      </c>
+    </row>
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
         <v>0.5894346477229786</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.6111311459431052</v>
       </c>
-      <c r="D3" t="n">
-        <v>0.5973170094137763</v>
-      </c>
-      <c r="E3" t="n">
-        <v>0.6071501283867727</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.5961076583562235</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Fold3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+      <c r="D3">
+        <v>0.5973170094137765</v>
+      </c>
+      <c r="E3">
+        <v>0.6071501283867732</v>
+      </c>
+      <c r="F3">
+        <v>0.5961076583562238</v>
+      </c>
+    </row>
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
         <v>0.6851471460323664</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.7015905023855717</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.7008424836406311</v>
       </c>
-      <c r="E4" t="n">
-        <v>0.6821426527106282</v>
-      </c>
-      <c r="F4" t="n">
-        <v>0.6822803686442911</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Fold4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+      <c r="E4">
+        <v>0.6821426527106285</v>
+      </c>
+      <c r="F4">
+        <v>0.6822803686442906</v>
+      </c>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
         <v>0.6737324813244909</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.7035464485482521</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.6946698465453498</v>
       </c>
-      <c r="E5" t="n">
-        <v>0.6755733586926432</v>
-      </c>
-      <c r="F5" t="n">
+      <c r="E5">
+        <v>0.6755733586926436</v>
+      </c>
+      <c r="F5">
         <v>0.6751437369244615</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Fold5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
         <v>0.6881056493421327</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.7032562241615186</v>
       </c>
-      <c r="D6" t="n">
-        <v>0.6927798669787192</v>
-      </c>
-      <c r="E6" t="n">
-        <v>0.7003061719089893</v>
-      </c>
-      <c r="F6" t="n">
-        <v>0.6978898662327341</v>
+      <c r="D6">
+        <v>0.6927798669787193</v>
+      </c>
+      <c r="E6">
+        <v>0.700306171908989</v>
+      </c>
+      <c r="F6">
+        <v>0.697889866232734</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:F6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
-    <row r="1">
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>Case1_Clinical</t>
-        </is>
-      </c>
-      <c r="C1" s="1" t="inlineStr">
-        <is>
-          <t>Case2_Clinical+AEC_prev</t>
-        </is>
-      </c>
-      <c r="D1" s="1" t="inlineStr">
-        <is>
-          <t>Case3_Clinical+AEC_new</t>
-        </is>
-      </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Case4_Clinical+AEC_prev+Scanner</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>Case5_Clinical+AEC_new+Scanner</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t>Fold1</t>
-        </is>
-      </c>
-      <c r="B2" t="n">
+    <row r="1" spans="1:6">
+      <c r="B1" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="F1" s="1" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="B2">
         <v>0.8175089712918659</v>
       </c>
-      <c r="C2" t="n">
+      <c r="C2">
         <v>0.8242374401913876</v>
       </c>
-      <c r="D2" t="n">
+      <c r="D2">
         <v>0.8303678229665071</v>
       </c>
-      <c r="E2" t="n">
+      <c r="E2">
         <v>0.8174342105263158</v>
       </c>
-      <c r="F2" t="n">
+      <c r="F2">
         <v>0.8250598086124402</v>
       </c>
     </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>Fold2</t>
-        </is>
-      </c>
-      <c r="B3" t="n">
+    <row r="3" spans="1:6">
+      <c r="A3" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B3">
         <v>0.7947069377990431</v>
       </c>
-      <c r="C3" t="n">
+      <c r="C3">
         <v>0.7918660287081339</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D3">
         <v>0.7944826555023923</v>
       </c>
-      <c r="E3" t="n">
+      <c r="E3">
         <v>0.796575956937799</v>
       </c>
-      <c r="F3" t="n">
+      <c r="F3">
         <v>0.7991178229665072</v>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
-        <is>
-          <t>Fold3</t>
-        </is>
-      </c>
-      <c r="B4" t="n">
+    <row r="4" spans="1:6">
+      <c r="A4" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="B4">
         <v>0.8357505980861244</v>
       </c>
-      <c r="C4" t="n">
+      <c r="C4">
         <v>0.8412081339712918</v>
       </c>
-      <c r="D4" t="n">
+      <c r="D4">
         <v>0.8447966507177033</v>
       </c>
-      <c r="E4" t="n">
+      <c r="E4">
         <v>0.8423295454545454</v>
       </c>
-      <c r="F4" t="n">
+      <c r="F4">
         <v>0.8466656698564593</v>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
-        <is>
-          <t>Fold4</t>
-        </is>
-      </c>
-      <c r="B5" t="n">
+    <row r="5" spans="1:6">
+      <c r="A5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="B5">
         <v>0.8489644970414201</v>
       </c>
-      <c r="C5" t="n">
+      <c r="C5">
         <v>0.857026627218935</v>
       </c>
-      <c r="D5" t="n">
+      <c r="D5">
         <v>0.8435650887573966</v>
       </c>
-      <c r="E5" t="n">
+      <c r="E5">
         <v>0.8548076923076924</v>
       </c>
-      <c r="F5" t="n">
+      <c r="F5">
         <v>0.8446745562130178</v>
       </c>
     </row>
-    <row r="6">
-      <c r="A6" s="1" t="inlineStr">
-        <is>
-          <t>Fold5</t>
-        </is>
-      </c>
-      <c r="B6" t="n">
+    <row r="6" spans="1:6">
+      <c r="A6" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="B6">
         <v>0.8493343195266272</v>
       </c>
-      <c r="C6" t="n">
+      <c r="C6">
         <v>0.8586538461538461</v>
       </c>
-      <c r="D6" t="n">
+      <c r="D6">
         <v>0.8630177514792899</v>
       </c>
-      <c r="E6" t="n">
+      <c r="E6">
         <v>0.8420857988165681</v>
       </c>
-      <c r="F6" t="n">
+      <c r="F6">
         <v>0.8446005917159763</v>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/연구코드/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/all/regression_results.xlsx
@@ -557,13 +557,13 @@
         <v>0.0208</v>
       </c>
       <c r="M2">
-        <v>0.7868000000000001</v>
+        <v>0.7223000000000001</v>
       </c>
       <c r="N2">
-        <v>0.3414</v>
+        <v>0.8754</v>
       </c>
       <c r="O2">
-        <v>0.9243</v>
+        <v>0.6749000000000001</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -604,13 +604,13 @@
         <v>0.0247</v>
       </c>
       <c r="M3">
-        <v>0.7846</v>
+        <v>0.7121</v>
       </c>
       <c r="N3">
-        <v>0.3447</v>
+        <v>0.9314</v>
       </c>
       <c r="O3">
-        <v>0.9204</v>
+        <v>0.6443</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -651,13 +651,13 @@
         <v>0.0229</v>
       </c>
       <c r="M4">
-        <v>0.7853</v>
+        <v>0.7201</v>
       </c>
       <c r="N4">
-        <v>0.3571</v>
+        <v>0.9127999999999999</v>
       </c>
       <c r="O4">
-        <v>0.9175</v>
+        <v>0.6606</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -698,13 +698,13 @@
         <v>0.0209</v>
       </c>
       <c r="M5">
-        <v>0.7883</v>
+        <v>0.7128</v>
       </c>
       <c r="N5">
-        <v>0.3758</v>
+        <v>0.9035</v>
       </c>
       <c r="O5">
-        <v>0.9156</v>
+        <v>0.6539</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -745,13 +745,13 @@
         <v>0.0182</v>
       </c>
       <c r="M6">
-        <v>0.7941</v>
+        <v>0.7436</v>
       </c>
       <c r="N6">
-        <v>0.3913</v>
+        <v>0.8786</v>
       </c>
       <c r="O6">
-        <v>0.9185</v>
+        <v>0.7018</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/all/regression_results.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="33">
   <si>
     <t>Hospital</t>
   </si>
@@ -82,6 +82,9 @@
   </si>
   <si>
     <t>Case 5 +AEC_new +Scanner</t>
+  </si>
+  <si>
+    <t>F:95.0/M:132.0</t>
   </si>
   <si>
     <t>Case1_Clinical</t>
@@ -547,23 +550,23 @@
       <c r="I2">
         <v>17.12</v>
       </c>
-      <c r="J2">
-        <v>100</v>
+      <c r="J2" t="s">
+        <v>22</v>
       </c>
       <c r="K2">
-        <v>0.8293</v>
+        <v>0.7427</v>
       </c>
       <c r="L2">
-        <v>0.0208</v>
+        <v>0.0188</v>
       </c>
       <c r="M2">
-        <v>0.7223000000000001</v>
+        <v>0.6762</v>
       </c>
       <c r="N2">
-        <v>0.8754</v>
+        <v>0.7647</v>
       </c>
       <c r="O2">
-        <v>0.6749000000000001</v>
+        <v>0.6491</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -594,23 +597,23 @@
       <c r="I3">
         <v>16.71</v>
       </c>
-      <c r="J3">
-        <v>100</v>
+      <c r="J3" t="s">
+        <v>22</v>
       </c>
       <c r="K3">
-        <v>0.8346</v>
+        <v>0.751</v>
       </c>
       <c r="L3">
-        <v>0.0247</v>
+        <v>0.0227</v>
       </c>
       <c r="M3">
-        <v>0.7121</v>
+        <v>0.7004</v>
       </c>
       <c r="N3">
-        <v>0.9314</v>
+        <v>0.7393999999999999</v>
       </c>
       <c r="O3">
-        <v>0.6443</v>
+        <v>0.6883</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -641,23 +644,23 @@
       <c r="I4">
         <v>16.93</v>
       </c>
-      <c r="J4">
-        <v>100</v>
+      <c r="J4" t="s">
+        <v>22</v>
       </c>
       <c r="K4">
-        <v>0.8352000000000001</v>
+        <v>0.7442</v>
       </c>
       <c r="L4">
-        <v>0.0229</v>
+        <v>0.028</v>
       </c>
       <c r="M4">
-        <v>0.7201</v>
+        <v>0.6374</v>
       </c>
       <c r="N4">
-        <v>0.9127999999999999</v>
+        <v>0.8274</v>
       </c>
       <c r="O4">
-        <v>0.6606</v>
+        <v>0.5794</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -688,23 +691,23 @@
       <c r="I5">
         <v>16.96</v>
       </c>
-      <c r="J5">
-        <v>100</v>
+      <c r="J5" t="s">
+        <v>22</v>
       </c>
       <c r="K5">
-        <v>0.8306</v>
+        <v>0.74</v>
       </c>
       <c r="L5">
-        <v>0.0209</v>
+        <v>0.0287</v>
       </c>
       <c r="M5">
-        <v>0.7128</v>
+        <v>0.6674</v>
       </c>
       <c r="N5">
-        <v>0.9035</v>
+        <v>0.7834</v>
       </c>
       <c r="O5">
-        <v>0.6539</v>
+        <v>0.6319</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -735,23 +738,23 @@
       <c r="I6">
         <v>17.11</v>
       </c>
-      <c r="J6">
-        <v>100</v>
+      <c r="J6" t="s">
+        <v>22</v>
       </c>
       <c r="K6">
-        <v>0.832</v>
+        <v>0.7311</v>
       </c>
       <c r="L6">
-        <v>0.0182</v>
+        <v>0.0291</v>
       </c>
       <c r="M6">
-        <v>0.7436</v>
+        <v>0.6762</v>
       </c>
       <c r="N6">
-        <v>0.8786</v>
+        <v>0.7522</v>
       </c>
       <c r="O6">
-        <v>0.7018</v>
+        <v>0.6529</v>
       </c>
     </row>
   </sheetData>
@@ -766,24 +769,24 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2">
         <v>0.6734344380268682</v>
@@ -798,38 +801,38 @@
         <v>0.6757323167354061</v>
       </c>
       <c r="F2">
-        <v>0.6585903231162162</v>
+        <v>0.6585903231162166</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
         <v>0.5894346477229786</v>
       </c>
       <c r="C3">
-        <v>0.6111311459431052</v>
+        <v>0.6111311459431051</v>
       </c>
       <c r="D3">
-        <v>0.5973170094137765</v>
+        <v>0.5973170094137766</v>
       </c>
       <c r="E3">
-        <v>0.6071501283867732</v>
+        <v>0.6071501283867731</v>
       </c>
       <c r="F3">
-        <v>0.5961076583562238</v>
+        <v>0.5961076583562237</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
         <v>0.6851471460323664</v>
       </c>
       <c r="C4">
-        <v>0.7015905023855717</v>
+        <v>0.7015905023855719</v>
       </c>
       <c r="D4">
         <v>0.7008424836406311</v>
@@ -838,12 +841,12 @@
         <v>0.6821426527106285</v>
       </c>
       <c r="F4">
-        <v>0.6822803686442906</v>
+        <v>0.6822803686442908</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
         <v>0.6737324813244909</v>
@@ -852,18 +855,18 @@
         <v>0.7035464485482521</v>
       </c>
       <c r="D5">
-        <v>0.6946698465453498</v>
+        <v>0.69466984654535</v>
       </c>
       <c r="E5">
-        <v>0.6755733586926436</v>
+        <v>0.6755733586926435</v>
       </c>
       <c r="F5">
-        <v>0.6751437369244615</v>
+        <v>0.6751437369244617</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
         <v>0.6881056493421327</v>
@@ -872,13 +875,13 @@
         <v>0.7032562241615186</v>
       </c>
       <c r="D6">
-        <v>0.6927798669787193</v>
+        <v>0.6927798669787192</v>
       </c>
       <c r="E6">
-        <v>0.700306171908989</v>
+        <v>0.7003061719089891</v>
       </c>
       <c r="F6">
-        <v>0.697889866232734</v>
+        <v>0.6978898662327342</v>
       </c>
     </row>
   </sheetData>
@@ -893,119 +896,119 @@
   <sheetData>
     <row r="1" spans="1:6">
       <c r="B1" s="1" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
     </row>
     <row r="2" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="B2">
-        <v>0.8175089712918659</v>
+        <v>0.7216931216931217</v>
       </c>
       <c r="C2">
-        <v>0.8242374401913876</v>
+        <v>0.7167044595616024</v>
       </c>
       <c r="D2">
-        <v>0.8303678229665071</v>
+        <v>0.7054421768707483</v>
       </c>
       <c r="E2">
-        <v>0.8174342105263158</v>
+        <v>0.7133030990173846</v>
       </c>
       <c r="F2">
-        <v>0.8250598086124402</v>
+        <v>0.6990173847316705</v>
       </c>
     </row>
     <row r="3" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="B3">
-        <v>0.7947069377990431</v>
+        <v>0.7459629186602871</v>
       </c>
       <c r="C3">
-        <v>0.7918660287081339</v>
+        <v>0.7593450956937799</v>
       </c>
       <c r="D3">
-        <v>0.7944826555023923</v>
+        <v>0.7618122009569378</v>
       </c>
       <c r="E3">
-        <v>0.796575956937799</v>
+        <v>0.7577751196172248</v>
       </c>
       <c r="F3">
-        <v>0.7991178229665072</v>
+        <v>0.7533642344497609</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="B4">
-        <v>0.8357505980861244</v>
+        <v>0.7541118421052632</v>
       </c>
       <c r="C4">
-        <v>0.8412081339712918</v>
+        <v>0.7648773923444976</v>
       </c>
       <c r="D4">
-        <v>0.8447966507177033</v>
+        <v>0.7612888755980861</v>
       </c>
       <c r="E4">
-        <v>0.8423295454545454</v>
+        <v>0.7584479665071769</v>
       </c>
       <c r="F4">
-        <v>0.8466656698564593</v>
+        <v>0.7380382775119617</v>
       </c>
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="1" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B5">
-        <v>0.8489644970414201</v>
+        <v>0.7217404306220095</v>
       </c>
       <c r="C5">
-        <v>0.857026627218935</v>
+        <v>0.7341507177033494</v>
       </c>
       <c r="D5">
-        <v>0.8435650887573966</v>
+        <v>0.7163576555023924</v>
       </c>
       <c r="E5">
-        <v>0.8548076923076924</v>
+        <v>0.6984150717703349</v>
       </c>
       <c r="F5">
-        <v>0.8446745562130178</v>
+        <v>0.6959479665071772</v>
       </c>
     </row>
     <row r="6" spans="1:6">
       <c r="A6" s="1" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B6">
-        <v>0.8493343195266272</v>
+        <v>0.770035885167464</v>
       </c>
       <c r="C6">
-        <v>0.8586538461538461</v>
+        <v>0.7801285885167464</v>
       </c>
       <c r="D6">
-        <v>0.8630177514792899</v>
+        <v>0.7763157894736841</v>
       </c>
       <c r="E6">
-        <v>0.8420857988165681</v>
+        <v>0.7719049043062202</v>
       </c>
       <c r="F6">
-        <v>0.8446005917159763</v>
+        <v>0.7689144736842105</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/all/regression_results.xlsx
@@ -801,7 +801,7 @@
         <v>0.6757323167354061</v>
       </c>
       <c r="F2">
-        <v>0.6585903231162166</v>
+        <v>0.6585903231162162</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -812,16 +812,16 @@
         <v>0.5894346477229786</v>
       </c>
       <c r="C3">
-        <v>0.6111311459431051</v>
+        <v>0.6111311459431052</v>
       </c>
       <c r="D3">
-        <v>0.5973170094137766</v>
+        <v>0.5973170094137765</v>
       </c>
       <c r="E3">
-        <v>0.6071501283867731</v>
+        <v>0.6071501283867732</v>
       </c>
       <c r="F3">
-        <v>0.5961076583562237</v>
+        <v>0.5961076583562238</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -832,7 +832,7 @@
         <v>0.6851471460323664</v>
       </c>
       <c r="C4">
-        <v>0.7015905023855719</v>
+        <v>0.7015905023855717</v>
       </c>
       <c r="D4">
         <v>0.7008424836406311</v>
@@ -841,7 +841,7 @@
         <v>0.6821426527106285</v>
       </c>
       <c r="F4">
-        <v>0.6822803686442908</v>
+        <v>0.6822803686442906</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -855,13 +855,13 @@
         <v>0.7035464485482521</v>
       </c>
       <c r="D5">
-        <v>0.69466984654535</v>
+        <v>0.6946698465453498</v>
       </c>
       <c r="E5">
-        <v>0.6755733586926435</v>
+        <v>0.6755733586926436</v>
       </c>
       <c r="F5">
-        <v>0.6751437369244617</v>
+        <v>0.6751437369244615</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -875,13 +875,13 @@
         <v>0.7032562241615186</v>
       </c>
       <c r="D6">
-        <v>0.6927798669787192</v>
+        <v>0.6927798669787193</v>
       </c>
       <c r="E6">
-        <v>0.7003061719089891</v>
+        <v>0.700306171908989</v>
       </c>
       <c r="F6">
-        <v>0.6978898662327342</v>
+        <v>0.697889866232734</v>
       </c>
     </row>
   </sheetData>

--- a/연구코드/results/regression/gangnam/all/regression_results.xlsx
+++ b/연구코드/results/regression/gangnam/all/regression_results.xlsx
@@ -45,7 +45,7 @@
     <t>Lin_RMSE</t>
   </si>
   <si>
-    <t>TAMA_threshold</t>
+    <t>SMI_threshold</t>
   </si>
   <si>
     <t>Log_AUC</t>
@@ -84,7 +84,7 @@
     <t>Case 5 +AEC_new +Scanner</t>
   </si>
   <si>
-    <t>F:95.0/M:132.0</t>
+    <t>F:38.46/M:46.87</t>
   </si>
   <si>
     <t>Case1_Clinical</t>
@@ -539,34 +539,34 @@
         <v>1365</v>
       </c>
       <c r="F2">
-        <v>0.662</v>
+        <v>0.4865</v>
       </c>
       <c r="G2">
-        <v>0.0367</v>
+        <v>0.0574</v>
       </c>
       <c r="H2">
-        <v>12.83</v>
+        <v>4.53</v>
       </c>
       <c r="I2">
-        <v>17.12</v>
+        <v>6.2</v>
       </c>
       <c r="J2" t="s">
         <v>22</v>
       </c>
       <c r="K2">
-        <v>0.7427</v>
+        <v>0.7707000000000001</v>
       </c>
       <c r="L2">
-        <v>0.0188</v>
+        <v>0.0284</v>
       </c>
       <c r="M2">
-        <v>0.6762</v>
+        <v>0.6462</v>
       </c>
       <c r="N2">
-        <v>0.7647</v>
+        <v>0.8653</v>
       </c>
       <c r="O2">
-        <v>0.6491</v>
+        <v>0.5733</v>
       </c>
     </row>
     <row r="3" spans="1:15">
@@ -586,34 +586,34 @@
         <v>1365</v>
       </c>
       <c r="F3">
-        <v>0.678</v>
+        <v>0.4997</v>
       </c>
       <c r="G3">
-        <v>0.0357</v>
+        <v>0.051</v>
       </c>
       <c r="H3">
-        <v>12.53</v>
+        <v>4.48</v>
       </c>
       <c r="I3">
-        <v>16.71</v>
+        <v>6.13</v>
       </c>
       <c r="J3" t="s">
         <v>22</v>
       </c>
       <c r="K3">
-        <v>0.751</v>
+        <v>0.7715</v>
       </c>
       <c r="L3">
-        <v>0.0227</v>
+        <v>0.029</v>
       </c>
       <c r="M3">
-        <v>0.7004</v>
+        <v>0.7062</v>
       </c>
       <c r="N3">
-        <v>0.7393999999999999</v>
+        <v>0.7479</v>
       </c>
       <c r="O3">
-        <v>0.6883</v>
+        <v>0.6924</v>
       </c>
     </row>
     <row r="4" spans="1:15">
@@ -627,40 +627,40 @@
         <v>19</v>
       </c>
       <c r="D4">
-        <v>14</v>
+        <v>42</v>
       </c>
       <c r="E4">
         <v>1365</v>
       </c>
       <c r="F4">
-        <v>0.6694</v>
+        <v>0.496</v>
       </c>
       <c r="G4">
-        <v>0.0385</v>
+        <v>0.0553</v>
       </c>
       <c r="H4">
-        <v>12.59</v>
+        <v>4.5</v>
       </c>
       <c r="I4">
-        <v>16.93</v>
+        <v>6.15</v>
       </c>
       <c r="J4" t="s">
         <v>22</v>
       </c>
       <c r="K4">
-        <v>0.7442</v>
+        <v>0.771</v>
       </c>
       <c r="L4">
-        <v>0.028</v>
+        <v>0.0265</v>
       </c>
       <c r="M4">
-        <v>0.6374</v>
+        <v>0.6813</v>
       </c>
       <c r="N4">
-        <v>0.8274</v>
+        <v>0.8038</v>
       </c>
       <c r="O4">
-        <v>0.5794</v>
+        <v>0.6407</v>
       </c>
     </row>
     <row r="5" spans="1:15">
@@ -680,34 +680,34 @@
         <v>1365</v>
       </c>
       <c r="F5">
-        <v>0.6682</v>
+        <v>0.4831</v>
       </c>
       <c r="G5">
-        <v>0.0318</v>
+        <v>0.0543</v>
       </c>
       <c r="H5">
-        <v>12.77</v>
+        <v>4.57</v>
       </c>
       <c r="I5">
-        <v>16.96</v>
+        <v>6.23</v>
       </c>
       <c r="J5" t="s">
         <v>22</v>
       </c>
       <c r="K5">
-        <v>0.74</v>
+        <v>0.7589</v>
       </c>
       <c r="L5">
-        <v>0.0287</v>
+        <v>0.0397</v>
       </c>
       <c r="M5">
-        <v>0.6674</v>
+        <v>0.6864</v>
       </c>
       <c r="N5">
-        <v>0.7834</v>
+        <v>0.7716</v>
       </c>
       <c r="O5">
-        <v>0.6319</v>
+        <v>0.6582</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -721,40 +721,40 @@
         <v>21</v>
       </c>
       <c r="D6">
-        <v>53</v>
+        <v>81</v>
       </c>
       <c r="E6">
         <v>1365</v>
       </c>
       <c r="F6">
-        <v>0.662</v>
+        <v>0.483</v>
       </c>
       <c r="G6">
-        <v>0.0353</v>
+        <v>0.0582</v>
       </c>
       <c r="H6">
-        <v>12.74</v>
+        <v>4.57</v>
       </c>
       <c r="I6">
-        <v>17.11</v>
+        <v>6.23</v>
       </c>
       <c r="J6" t="s">
         <v>22</v>
       </c>
       <c r="K6">
-        <v>0.7311</v>
+        <v>0.7564</v>
       </c>
       <c r="L6">
-        <v>0.0291</v>
+        <v>0.0382</v>
       </c>
       <c r="M6">
-        <v>0.6762</v>
+        <v>0.6857</v>
       </c>
       <c r="N6">
-        <v>0.7522</v>
+        <v>0.7862</v>
       </c>
       <c r="O6">
-        <v>0.6529</v>
+        <v>0.6524</v>
       </c>
     </row>
   </sheetData>
@@ -789,19 +789,19 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>0.6734344380268682</v>
+        <v>0.524497877572347</v>
       </c>
       <c r="C2">
-        <v>0.6702630916927976</v>
+        <v>0.5070323702002385</v>
       </c>
       <c r="D2">
-        <v>0.6616180339311908</v>
+        <v>0.5146768281469007</v>
       </c>
       <c r="E2">
-        <v>0.6757323167354061</v>
+        <v>0.4949720048302599</v>
       </c>
       <c r="F2">
-        <v>0.6585903231162162</v>
+        <v>0.50257343322613</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -809,19 +809,19 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.5894346477229786</v>
+        <v>0.4207233649255953</v>
       </c>
       <c r="C3">
-        <v>0.6111311459431052</v>
+        <v>0.4376316572367405</v>
       </c>
       <c r="D3">
-        <v>0.5973170094137765</v>
+        <v>0.4189784482217425</v>
       </c>
       <c r="E3">
-        <v>0.6071501283867732</v>
+        <v>0.4232160853209845</v>
       </c>
       <c r="F3">
-        <v>0.5961076583562238</v>
+        <v>0.407202078172573</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -829,19 +829,19 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>0.6851471460323664</v>
+        <v>0.5146235556264914</v>
       </c>
       <c r="C4">
-        <v>0.7015905023855717</v>
+        <v>0.5319220221525216</v>
       </c>
       <c r="D4">
-        <v>0.7008424836406311</v>
+        <v>0.5311002358493737</v>
       </c>
       <c r="E4">
-        <v>0.6821426527106285</v>
+        <v>0.517937427242406</v>
       </c>
       <c r="F4">
-        <v>0.6822803686442906</v>
+        <v>0.5243990851600988</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -849,19 +849,19 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>0.6737324813244909</v>
+        <v>0.4159679754390594</v>
       </c>
       <c r="C5">
-        <v>0.7035464485482521</v>
+        <v>0.4484954178330224</v>
       </c>
       <c r="D5">
-        <v>0.6946698465453498</v>
+        <v>0.4463706585314642</v>
       </c>
       <c r="E5">
-        <v>0.6755733586926436</v>
+        <v>0.4199493509019406</v>
       </c>
       <c r="F5">
-        <v>0.6751437369244615</v>
+        <v>0.4233693135480506</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -869,19 +869,19 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>0.6881056493421327</v>
+        <v>0.5568727790710715</v>
       </c>
       <c r="C6">
-        <v>0.7032562241615186</v>
+        <v>0.5733388842885329</v>
       </c>
       <c r="D6">
-        <v>0.6927798669787193</v>
+        <v>0.5687742844189441</v>
       </c>
       <c r="E6">
-        <v>0.700306171908989</v>
+        <v>0.5592839032038186</v>
       </c>
       <c r="F6">
-        <v>0.697889866232734</v>
+        <v>0.5574291835278398</v>
       </c>
     </row>
   </sheetData>
@@ -916,19 +916,19 @@
         <v>28</v>
       </c>
       <c r="B2">
-        <v>0.7216931216931217</v>
+        <v>0.7996413199426112</v>
       </c>
       <c r="C2">
-        <v>0.7167044595616024</v>
+        <v>0.8068149210903873</v>
       </c>
       <c r="D2">
-        <v>0.7054421768707483</v>
+        <v>0.8029411764705882</v>
       </c>
       <c r="E2">
-        <v>0.7133030990173846</v>
+        <v>0.8048780487804879</v>
       </c>
       <c r="F2">
-        <v>0.6990173847316705</v>
+        <v>0.8073170731707316</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -936,19 +936,19 @@
         <v>29</v>
       </c>
       <c r="B3">
-        <v>0.7459629186602871</v>
+        <v>0.8076757532281205</v>
       </c>
       <c r="C3">
-        <v>0.7593450956937799</v>
+        <v>0.8038020086083214</v>
       </c>
       <c r="D3">
-        <v>0.7618122009569378</v>
+        <v>0.8028694404591106</v>
       </c>
       <c r="E3">
-        <v>0.7577751196172248</v>
+        <v>0.8076040172166428</v>
       </c>
       <c r="F3">
-        <v>0.7533642344497609</v>
+        <v>0.7977761836441893</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -956,19 +956,19 @@
         <v>30</v>
       </c>
       <c r="B4">
-        <v>0.7541118421052632</v>
+        <v>0.7614777618364419</v>
       </c>
       <c r="C4">
-        <v>0.7648773923444976</v>
+        <v>0.7614060258249641</v>
       </c>
       <c r="D4">
-        <v>0.7612888755980861</v>
+        <v>0.7550932568149211</v>
       </c>
       <c r="E4">
-        <v>0.7584479665071769</v>
+        <v>0.7439024390243901</v>
       </c>
       <c r="F4">
-        <v>0.7380382775119617</v>
+        <v>0.733142037302726</v>
       </c>
     </row>
     <row r="5" spans="1:6">
@@ -976,19 +976,19 @@
         <v>31</v>
       </c>
       <c r="B5">
-        <v>0.7217404306220095</v>
+        <v>0.750573888091822</v>
       </c>
       <c r="C5">
-        <v>0.7341507177033494</v>
+        <v>0.751506456241033</v>
       </c>
       <c r="D5">
-        <v>0.7163576555023924</v>
+        <v>0.753012912482066</v>
       </c>
       <c r="E5">
-        <v>0.6984150717703349</v>
+        <v>0.7191535150645624</v>
       </c>
       <c r="F5">
-        <v>0.6959479665071772</v>
+        <v>0.7167862266857962</v>
       </c>
     </row>
     <row r="6" spans="1:6">
@@ -996,19 +996,19 @@
         <v>32</v>
       </c>
       <c r="B6">
-        <v>0.770035885167464</v>
+        <v>0.7340863881784598</v>
       </c>
       <c r="C6">
-        <v>0.7801285885167464</v>
+        <v>0.7340863881784598</v>
       </c>
       <c r="D6">
-        <v>0.7763157894736841</v>
+        <v>0.7408354646206309</v>
       </c>
       <c r="E6">
-        <v>0.7719049043062202</v>
+        <v>0.7190963341858483</v>
       </c>
       <c r="F6">
-        <v>0.7689144736842105</v>
+        <v>0.7269110542767832</v>
       </c>
     </row>
   </sheetData>
